--- a/PCB_Project/Project Outputs for uz_per_torque_kistler_burster/Rev1/BOM/BOM_uz_per_torque_kistler_burster_[No Variations]_Rev1.xlsx
+++ b/PCB_Project/Project Outputs for uz_per_torque_kistler_burster/Rev1/BOM/BOM_uz_per_torque_kistler_burster_[No Variations]_Rev1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nina Diringer\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D0EF751-A110-48FE-910F-95165AD7ED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4961DEC0-959B-43E1-AE2B-6E45C06D15C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{523E3957-644D-4C65-AD7C-0FE8CC39AC3B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11325" xr2:uid="{903B8FF1-607F-40F2-85EE-65CC76E38873}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_uz_per_torque_kistler_burst" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
   <si>
     <t>Designator</t>
   </si>
@@ -47,15 +47,15 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Manufacturer Part Number</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
     <t>Supplier Part Number 1</t>
   </si>
   <si>
-    <t>Supplier Part Number 2</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>Footprint</t>
   </si>
   <si>
@@ -65,9 +65,6 @@
     <t>Supplier 1</t>
   </si>
   <si>
-    <t>Supplier 2</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -77,15 +74,15 @@
     <t>DC Power Receptacle 260℃ Brass -20℃~+70℃ 2.5mm 6.5mm 2.5A 24V SMD AC/DC Power Connectors ROHS</t>
   </si>
   <si>
+    <t>DC-005-5A-2.5-SMT</t>
+  </si>
+  <si>
+    <t>XKB Connectivity</t>
+  </si>
+  <si>
     <t>C319133</t>
   </si>
   <si>
-    <t>=Manufacturer Part Number</t>
-  </si>
-  <si>
-    <t>DC-005-5A-2.5-SMT</t>
-  </si>
-  <si>
     <t>LCSC</t>
   </si>
   <si>
@@ -95,21 +92,33 @@
     <t>15 Female D-Sub Shrouded 2 3A -40℃~+85℃ Plugin D-Sub/DVI/HDMI Connectors ROHS</t>
   </si>
   <si>
+    <t>SUB-DRBF-607A-002</t>
+  </si>
+  <si>
+    <t>Nextron(Nextronics Engineering)</t>
+  </si>
+  <si>
     <t>C2846090</t>
   </si>
   <si>
+    <t>PCB - MISC - DSUB15</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>PCB - MISC - DSUB15</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
     <t>1 Inner bore BNC Board Edge 4GHz 50Ω Plugin RF Connectors / Coaxial Connectors ROHS</t>
   </si>
   <si>
+    <t>5227661-1</t>
+  </si>
+  <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
     <t>C305920</t>
   </si>
   <si>
@@ -122,6 +131,12 @@
     <t>RJ45 RJReceptacle 1 Yes cat5 Without LED SMD Ethernet Connectors/Modular Connectors (RJ45 RJ11) ROHS</t>
   </si>
   <si>
+    <t>6339160-1</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
     <t>=LCSC Part Number</t>
   </si>
   <si>
@@ -134,6 +149,9 @@
     <t>9 Female D-Sub Shrouded 2 3A -50℃~+105℃ Plugin D-Sub/DVI/HDMI Connectors ROHS</t>
   </si>
   <si>
+    <t>D-DMR009PF-D002</t>
+  </si>
+  <si>
     <t>C141882</t>
   </si>
   <si>
@@ -146,24 +164,21 @@
     <t>FCR7350B, 1000V, 24A, BLACK</t>
   </si>
   <si>
+    <t>FCR7350B</t>
+  </si>
+  <si>
+    <t>Cliff</t>
+  </si>
+  <si>
     <t>3185-FCR7350B-ND</t>
   </si>
   <si>
-    <t>1854507</t>
-  </si>
-  <si>
-    <t>FCR7350B, PCB mount 4mm jack, BLACK</t>
-  </si>
-  <si>
     <t>FCR7350</t>
   </si>
   <si>
     <t>Digi-Key</t>
   </si>
   <si>
-    <t>Farnell</t>
-  </si>
-  <si>
     <t>PCB mount 4mm jack, Black	FCR7350B, 1000V, 24A</t>
   </si>
   <si>
@@ -173,24 +188,21 @@
     <t>SMD resistor E24 series, SMD resistor E24 series 470 kOhms 100-200 mW 0603 1%</t>
   </si>
   <si>
+    <t>RC0603JR-070RL, 0603WAD2002T5E, 0603WAD2702T5E, 0603WAD1001T5E</t>
+  </si>
+  <si>
+    <t>YAGEO, UNI-ROYAL(Uniroyal Elec)</t>
+  </si>
+  <si>
     <t>603-RC0603JR-070RL, =LCSC Part Number</t>
   </si>
   <si>
-    <t>=LCSC Part Number, [NoValue]</t>
-  </si>
-  <si>
-    <t>=Value</t>
-  </si>
-  <si>
     <t>RES 0603_1608</t>
   </si>
   <si>
     <t>Mouser, LCSC/JLCPCB</t>
   </si>
   <si>
-    <t>LCSC, [NoValue]</t>
-  </si>
-  <si>
     <t>0R, 20k, 27k, 1k</t>
   </si>
   <si>
@@ -200,7 +212,10 @@
     <t>Field to put in a serial number</t>
   </si>
   <si>
-    <t>Serial #</t>
+    <t>Serial Number</t>
+  </si>
+  <si>
+    <t>PCB Manufacturer</t>
   </si>
   <si>
     <t>SERIAL</t>
@@ -212,6 +227,12 @@
     <t>SPST Black Flat dial, raised type 2.54mm 1 SMD DIP Switches</t>
   </si>
   <si>
+    <t>DSIC01LSGET</t>
+  </si>
+  <si>
+    <t>Dongguan Guangzhu Industrial</t>
+  </si>
+  <si>
     <t>C54948</t>
   </si>
   <si>
@@ -224,6 +245,9 @@
     <t>Pin Header, 2.54mm, 1 Pin</t>
   </si>
   <si>
+    <t>4-103327-3</t>
+  </si>
+  <si>
     <t>571-4-103327-3</t>
   </si>
   <si>
@@ -240,6 +264,9 @@
   </si>
   <si>
     <t>IPL1-108-01-L-D-RA-K</t>
+  </si>
+  <si>
+    <t>SAMTEC</t>
   </si>
   <si>
     <t>Samtec</t>
@@ -618,18 +645,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF876985-394E-4CFD-99B5-576583060CCF}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2905A7EE-1EAA-40A4-865C-9CE94E97400A}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.21875" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" customWidth="1"/>
-    <col min="5" max="10" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="97.7109375" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="9" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -657,51 +684,49 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1"/>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>20</v>
@@ -710,274 +735,260 @@
         <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G8" s="1">
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G10" s="1">
         <v>2</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="1"/>
+        <v>74</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/PCB_Project/Project Outputs for uz_per_torque_kistler_burster/Rev1/BOM/BOM_uz_per_torque_kistler_burster_[No Variations]_Rev1.xlsx
+++ b/PCB_Project/Project Outputs for uz_per_torque_kistler_burster/Rev1/BOM/BOM_uz_per_torque_kistler_burster_[No Variations]_Rev1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nina Diringer\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4961DEC0-959B-43E1-AE2B-6E45C06D15C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04A3C01C-CB88-4543-841B-A626AE9D172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11325" xr2:uid="{903B8FF1-607F-40F2-85EE-65CC76E38873}"/>
+    <workbookView xWindow="-28020" yWindow="870" windowWidth="21600" windowHeight="11325" xr2:uid="{D11413F1-1E93-45E7-8C16-CCA90DD9A859}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_uz_per_torque_kistler_burst" sheetId="1" r:id="rId1"/>
@@ -645,18 +645,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2905A7EE-1EAA-40A4-865C-9CE94E97400A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F000129D-A8BB-4CAE-8DB7-63863E8FF170}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="97.7109375" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
-    <col min="6" max="9" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.21875" customWidth="1"/>
+    <col min="2" max="2" width="94.6640625" customWidth="1"/>
+    <col min="3" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="6" max="9" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -685,7 +685,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -712,7 +712,7 @@
       </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -741,7 +741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -768,7 +768,7 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -795,7 +795,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
@@ -824,7 +824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
@@ -853,7 +853,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
@@ -882,7 +882,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>55</v>
       </c>
@@ -905,7 +905,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -934,7 +934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -963,7 +963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>72</v>
       </c>
